--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/KENTUCKY_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/KENTUCKY_2018.xlsx
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C106">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C146">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C222">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C552">
@@ -15781,7 +15781,7 @@
         <v>35</v>
       </c>
       <c r="D857">
-        <v>0.009050943884147919</v>
+        <v>0.00905094388414792</v>
       </c>
     </row>
     <row r="858">
